--- a/r_test/plot_metrics/Plot_Metrics_Summary.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Summary.xlsx
@@ -1,21 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\GitHub\UWW200_Master_Thesis_public\r_test\plot_metrics\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE336DC9-A7A7-4D24-9EA6-DFBB09158FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1180" yWindow="2660" windowWidth="37220" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Testsite</t>
+  </si>
+  <si>
+    <t>simpson_index_PC</t>
+  </si>
+  <si>
+    <t>Unique_Plant_Cummunities</t>
+  </si>
+  <si>
+    <t>simpson_index_HT</t>
+  </si>
+  <si>
+    <t>Unique_Habitat_Types</t>
+  </si>
+  <si>
+    <t>simpson_index_TAX</t>
+  </si>
+  <si>
+    <t>Unique_Plant_Types</t>
+  </si>
+  <si>
+    <t>AN_TJ_1</t>
+  </si>
+  <si>
+    <t>AN_TJ_2</t>
+  </si>
+  <si>
+    <t>ATQ_VK_1</t>
+  </si>
+  <si>
+    <t>BRW_PW_1</t>
+  </si>
+  <si>
+    <t>BRW_VS_1</t>
+  </si>
+  <si>
+    <t>FLXTWRZONA_SD_1</t>
+  </si>
+  <si>
+    <t>FLXTWRZONA_SD_2</t>
+  </si>
+  <si>
+    <t>FLXTWRZONA_SD_3</t>
+  </si>
+  <si>
+    <t>FLXTWRZONA_SD_4</t>
+  </si>
+  <si>
+    <t>FRST_AK_2</t>
+  </si>
+  <si>
+    <t>FRST_AK_3</t>
+  </si>
+  <si>
+    <t>PRUAIR_DW_1</t>
+  </si>
+  <si>
+    <t>PRUARC_DW_1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +134,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +186,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +220,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,52 +431,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Testsite</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>simpson_index_PC</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Unique_Plant_Cummunities</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>simpson_index_HT</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Unique_Habitat_Types</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>simpson_index_TAX</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Unique_Plant_Types</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AN_TJ_1</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0.74</v>
@@ -410,17 +484,15 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>0.9649793423495444</v>
+        <v>0.96497934234954441</v>
       </c>
       <c r="G2">
         <v>79</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AN_TJ_2</t>
-        </is>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0.72</v>
@@ -435,95 +507,87 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>0.9090484890515731</v>
+        <v>0.90904848905157309</v>
       </c>
       <c r="G3">
         <v>68</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ATQ_VK_1</t>
-        </is>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>0.846938775510204</v>
+        <v>0.84693877551020402</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4">
-        <v>0.7551020408163265</v>
+        <v>0.75510204081632648</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4">
-        <v>0.9551961759026579</v>
+        <v>0.95519617590265793</v>
       </c>
       <c r="G4">
         <v>142</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BRW_PW_1</t>
-        </is>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>0.9054178145087236</v>
+        <v>0.90541781450872361</v>
       </c>
       <c r="C5">
         <v>12</v>
       </c>
       <c r="D5">
-        <v>0.3599632690541781</v>
+        <v>0.35996326905417808</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>0.8831066214540184</v>
+        <v>0.88310662145401841</v>
       </c>
       <c r="G5">
         <v>73</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BRW_VS_1</t>
-        </is>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>0.9288194444444444</v>
+        <v>0.92881944444444442</v>
       </c>
       <c r="C6">
         <v>16</v>
       </c>
       <c r="D6">
-        <v>0.5416666666666666</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>0.9147231160400233</v>
+        <v>0.91472311604002332</v>
       </c>
       <c r="G6">
         <v>51</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_1</t>
-        </is>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>0.675</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -541,11 +605,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_2</t>
-        </is>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
       </c>
       <c r="B8">
         <v>0.9211111111111111</v>
@@ -554,57 +616,53 @@
         <v>17</v>
       </c>
       <c r="D8">
-        <v>0.6111111111111112</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>0.866422721726833</v>
+        <v>0.86642272172683299</v>
       </c>
       <c r="G8">
         <v>46</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_3</t>
-        </is>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>0.8644444444444445</v>
+        <v>0.86444444444444446</v>
       </c>
       <c r="C9">
         <v>9</v>
       </c>
       <c r="D9">
-        <v>0.4444444444444444</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>0.8978286596744133</v>
+        <v>0.89782865967441328</v>
       </c>
       <c r="G9">
         <v>44</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FLXTWRZONA_SD_4</t>
-        </is>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>0.8311111111111111</v>
+        <v>0.83111111111111113</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.4444444444444444</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -616,11 +674,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FRST_AK_2</t>
-        </is>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
       </c>
       <c r="B11">
         <v>0.66</v>
@@ -635,51 +691,47 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>0.9467902933614543</v>
+        <v>0.94679029336145426</v>
       </c>
       <c r="G11">
         <v>88</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FRST_AK_3</t>
-        </is>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>0.775623268698061</v>
+        <v>0.77562326869806097</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>0.5983379501385042</v>
+        <v>0.59833795013850422</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0.9524506793936585</v>
+        <v>0.95245067939365846</v>
       </c>
       <c r="G12">
         <v>133</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PRUAIR_DW_1</t>
-        </is>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>0.8544</v>
+        <v>0.85440000000000005</v>
       </c>
       <c r="C13">
         <v>8</v>
       </c>
       <c r="D13">
-        <v>0.5212620027434842</v>
+        <v>0.52126200274348422</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -691,20 +743,18 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PRUARC_DW_1</t>
-        </is>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>0.8941736028537456</v>
+        <v>0.89417360285374559</v>
       </c>
       <c r="C14">
         <v>10</v>
       </c>
       <c r="D14">
-        <v>0.5350772889417361</v>
+        <v>0.53507728894173612</v>
       </c>
       <c r="E14">
         <v>5</v>

--- a/r_test/plot_metrics/Plot_Metrics_Summary.xlsx
+++ b/r_test/plot_metrics/Plot_Metrics_Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\GitHub\UWW200_Master_Thesis_public\r_test\plot_metrics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrickangst/Documents/GitHub/UWW200_Master_Thesis_public/r_test/plot_metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE336DC9-A7A7-4D24-9EA6-DFBB09158FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FA146F-B3C4-EB4E-92BE-4B9E3D1944BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="2660" windowWidth="37220" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1180" yWindow="2660" windowWidth="37220" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,6 @@
     <t>simpson_index_TAX</t>
   </si>
   <si>
-    <t>Unique_Plant_Types</t>
-  </si>
-  <si>
     <t>AN_TJ_1</t>
   </si>
   <si>
@@ -80,6 +77,9 @@
   </si>
   <si>
     <t>PRUARC_DW_1</t>
+  </si>
+  <si>
+    <t>Unique_Plant_Species</t>
   </si>
 </sst>
 </file>
@@ -433,18 +433,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,12 +464,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
       </c>
       <c r="B2">
         <v>0.74</v>
@@ -490,9 +490,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0.72</v>
@@ -513,9 +513,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0.84693877551020402</v>
@@ -536,9 +536,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0.90541781450872361</v>
@@ -559,9 +559,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>0.92881944444444442</v>
@@ -582,9 +582,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>0.67500000000000004</v>
@@ -605,9 +605,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>0.9211111111111111</v>
@@ -628,9 +628,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0.86444444444444446</v>
@@ -651,9 +651,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>0.83111111111111113</v>
@@ -674,9 +674,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0.66</v>
@@ -697,9 +697,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>0.77562326869806097</v>
@@ -720,9 +720,9 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>0.85440000000000005</v>
@@ -743,9 +743,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>0.89417360285374559</v>
